--- a/education_forms/045_literacy_letter_id_sounds--education_forms.xlsx
+++ b/education_forms/045_literacy_letter_id_sounds--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>correct_letter_id_sound</t>
+          <t>correct_letter_id_sound_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>correct letter id sound</t>
+          <t>Correct Letter Id Sound 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>correct_sound_ids</t>
+          <t>correct_sound_ids_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>correct sound ids</t>
+          <t>Correct Sound Ids 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>correct_sound_id</t>
+          <t>correct_sound_id_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>correct sound id</t>
+          <t>Correct Sound Id 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1840,7 +1840,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>correct_letter_id_sound_choices</t>
+          <t>correct_letter_id_sound_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>correct_letter_id_sound_choices</t>
+          <t>correct_letter_id_sound_2_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>correct_letter_id_sound_choices</t>
+          <t>correct_letter_id_sound_2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2044,7 +2044,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>correct_sound_ids_choices</t>
+          <t>correct_sound_ids_2_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2061,7 +2061,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>correct_sound_ids_choices</t>
+          <t>correct_sound_ids_2_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2078,7 +2078,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>correct_sound_ids_choices</t>
+          <t>correct_sound_ids_2_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2299,7 +2299,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>correct_sound_id_choices</t>
+          <t>correct_sound_id_2_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2316,7 +2316,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>correct_sound_id_choices</t>
+          <t>correct_sound_id_2_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2333,7 +2333,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>correct_sound_id_choices</t>
+          <t>correct_sound_id_2_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
